--- a/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.74%1,001,000</t>
+          <t>8.02%1,001,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.74%</t>
+          <t>8.02%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>13865</v>
+        <v>13450</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.61%235,000</t>
+          <t>6.69%205,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>6.69%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>235000</v>
+        <v>205000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.22%1,116,000</t>
+          <t>6.48%1,116,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.22%</t>
+          <t>6.48%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.92%465,000</t>
+          <t>5.97%465,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>5.97%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.89%1,161,000</t>
+          <t>5.92%1,161,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.64%2,482,000</t>
+          <t>5.56%2,482,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.64%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.37%1,074,000</t>
+          <t>5.45%1,074,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7810</v>
+        <v>7150</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.35%293,000</t>
+          <t>5.09%293,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.09%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1265</v>
+        <v>1185</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.82%1,630,000</t>
+          <t>4.69%1,630,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.69%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.44%542</t>
+          <t>-3.14%525</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.44%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.49%2,753,000</t>
+          <t>3.51%2,753,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.35%658</t>
+          <t>-4.41%629</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>658</v>
+        <v>629</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.43%2,231,000</t>
+          <t>3.41%2,231,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,34 +1175,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.55%131</t>
+          <t>+1.62%188.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>131</v>
+        <v>188.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.33%10,877,000</t>
+          <t>3.32%7,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>10877000</v>
+        <v>7245000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5290</v>
+        <v>5045</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.31%268,000</t>
+          <t>3.28%268,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.92%185.5</t>
+          <t>-8.4%120</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>185.5</v>
+        <v>120</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.14%7,245,000</t>
+          <t>3.17%10,877,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7245000</v>
+        <v>10877000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:38</t>
+          <t>2026-09-03 21:25:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.28%237.5</t>
+          <t>-6.95%221</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>237.5</v>
+        <v>221</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.02%5,445,000</t>
+          <t>2.92%5,445,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2%459</t>
+          <t>-9.91%413.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2%</t>
+          <t>-9.91%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>459</v>
+        <v>413.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.88%2,682,000</t>
+          <t>2.69%2,682,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.71%968,000</t>
+          <t>2.54%968,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-1.61%5800</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5895</v>
+        <v>5800</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.26%164,000</t>
+          <t>2.31%164,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.75%4200</t>
+          <t>0%4050</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.09%847</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>847</v>
+        <v>1760</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.67%844,013</t>
+          <t>1.63%382,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>844013</v>
+        <v>382000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>-8.5%775</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1730</v>
+        <v>775</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.54%382,000</t>
+          <t>1.59%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>382000</v>
+        <v>844013</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.45%145,000</t>
+          <t>1.53%145,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.40%229,675</t>
+          <t>1.38%229,675</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>-8.48%464</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-8.48%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.18%1,000,000</t>
+          <t>1.13%1,000,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.88%3395</t>
+          <t>-5.08%299</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3395</v>
+        <v>299</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.50%63,000</t>
+          <t>0.48%659,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>63000</v>
+        <v>659000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+4.83%315</t>
+          <t>-8.1%3120</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>315</v>
+        <v>3120</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.49%659,000</t>
+          <t>0.48%63,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>659000</v>
+        <v>63000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.55%536</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>536</v>
+        <v>17850</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.47%373,000</t>
+          <t>0.48%11,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>373000</v>
+        <v>11000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%1010</t>
+          <t>-4.48%512</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1010</v>
+        <v>512</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.46%196,000</t>
+          <t>0.46%373,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>196000</v>
+        <v>373000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>-3.86%971</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-3.86%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17725</v>
+        <v>971</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.46%11,000</t>
+          <t>0.46%196,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>11000</v>
+        <v>196000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:39</t>
+          <t>2026-09-03 21:25:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5770</v>
+        <v>5615</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.7%361.5</t>
+          <t>-3.04%350.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>361.5</v>
+        <v>350.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%721</t>
+          <t>-1.25%712</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.42%250,000</t>
+          <t>0.43%250,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.55%1340</t>
+          <t>-1.22%89.1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1340</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.42%134,000</t>
+          <t>0.42%1,957,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>134000</v>
+        <v>1957000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-6.16%686</t>
+          <t>-2.99%1300</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.16%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>686</v>
+        <v>1300</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.42%261,000</t>
+          <t>0.42%134,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>261000</v>
+        <v>134000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-3.22%90.2</t>
+          <t>-7%638</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>90.2</v>
+        <v>638</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.41%1,957,000</t>
+          <t>0.40%261,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1957000</v>
+        <v>261000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>+0.98%1035</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1410</v>
+        <v>1035</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.37%113,000</t>
+          <t>0.39%155,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>113000</v>
+        <v>155000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-6.82%1025</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.82%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1025</v>
+        <v>2015</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.37%155,000</t>
+          <t>0.37%76,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>155000</v>
+        <v>76000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1975</v>
+        <v>1345</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.35%76,000</t>
+          <t>0.37%113,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>76000</v>
+        <v>113000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.07%1420</t>
+          <t>-5.28%1345</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-5.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1420</v>
+        <v>1345</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:40</t>
+          <t>2026-09-03 21:25:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.61%149.5</t>
+          <t>-1.67%147</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>149.5</v>
+        <v>147</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">

--- a/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:49</t>
+          <t>2026-09-03 21:40:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:50</t>
+          <t>2026-09-03 21:40:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:51</t>
+          <t>2026-09-03 21:40:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:29</t>
+          <t>2026-09-03 22:32:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:31</t>
+          <t>2026-09-03 22:32:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:32</t>
+          <t>2026-09-03 22:32:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:34</t>
+          <t>2026-09-03 22:45:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:36</t>
+          <t>2026-09-03 22:45:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:37</t>
+          <t>2026-09-03 22:45:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">

--- a/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:00</t>
+          <t>2026-09-03 23:01:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:01</t>
+          <t>2026-09-03 23:01:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:03</t>
+          <t>2026-09-03 23:01:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
